--- a/Estadisticas.xlsx
+++ b/Estadisticas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -462,6 +462,31 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Felipe cruz</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Solitario</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Difícil</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Perdió</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
